--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 15,11</t>
+          <t>-13,31; 15,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 29,72</t>
+          <t>-9,12; 28,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 11,76</t>
+          <t>-20,3; 12,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,22</t>
+          <t>-3,85; 1,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 62,32</t>
+          <t>-34,8; 65,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 70,96</t>
+          <t>-13,12; 66,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 23,09</t>
+          <t>-32,64; 25,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,24</t>
+          <t>-3,86; 1,27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 6,54</t>
+          <t>-22,28; 5,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 13,9</t>
+          <t>-16,37; 13,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 21,64</t>
+          <t>-4,86; 21,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,85</t>
+          <t>2,03; 11,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 16,28</t>
+          <t>-39,95; 12,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 36,72</t>
+          <t>-31,54; 38,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 56,58</t>
+          <t>-9,83; 55,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,31</t>
+          <t>2,09; 13,23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 17,29</t>
+          <t>-8,79; 17,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 20,33</t>
+          <t>-10,6; 19,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 14,4</t>
+          <t>-15,28; 14,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -0,02</t>
+          <t>-9,08; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 62,4</t>
+          <t>-22,13; 63,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 54,56</t>
+          <t>-20,03; 54,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 46,66</t>
+          <t>-34,16; 46,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -0,06</t>
+          <t>-9,19; -0,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 7,69</t>
+          <t>-18,33; 9,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 15,49</t>
+          <t>-20,28; 13,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 25,04</t>
+          <t>-11,09; 25,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 10,68</t>
+          <t>-6,34; 9,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 17,28</t>
+          <t>-31,77; 20,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 37,42</t>
+          <t>-35,68; 32,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 59,49</t>
+          <t>-17,88; 61,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 12,5</t>
+          <t>-6,37; 10,75</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 64,54</t>
+          <t>-7,97; 64,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 30,75</t>
+          <t>-22,73; 28,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 25,26</t>
+          <t>-13,14; 24,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,28</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 434,91</t>
+          <t>-17,32; 439,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 79,03</t>
+          <t>-38,17; 76,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 82,85</t>
+          <t>-27,29; 79,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,84</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 10,43</t>
+          <t>-18,96; 9,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 13,16</t>
+          <t>-23,77; 11,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 28,63</t>
+          <t>-11,13; 29,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 3,91</t>
+          <t>-11,32; 4,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 31,93</t>
+          <t>-39,78; 27,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 26,85</t>
+          <t>-35,32; 22,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 141,06</t>
+          <t>-29,34; 134,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 4,0</t>
+          <t>-11,63; 4,58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 5,53</t>
+          <t>-16,48; 5,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 10,83</t>
+          <t>-11,15; 10,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 6,21</t>
+          <t>-13,1; 7,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,78</t>
+          <t>-4,69; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 16,46</t>
+          <t>-34,87; 13,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 22,53</t>
+          <t>-19,4; 22,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 20,97</t>
+          <t>-33,79; 24,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,06</t>
+          <t>-4,82; 4,49</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 7,22</t>
+          <t>-15,68; 7,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 1,49</t>
+          <t>-16,47; 2,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 9,23</t>
+          <t>-10,21; 8,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 3,55</t>
+          <t>-9,86; 3,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 17,79</t>
+          <t>-30,43; 18,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 4,36</t>
+          <t>-38,8; 8,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 26,91</t>
+          <t>-24,2; 24,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 4,04</t>
+          <t>-10,44; 3,62</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,74</t>
+          <t>-8,11; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,66</t>
+          <t>-6,86; 3,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,87</t>
+          <t>-3,21; 6,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,48</t>
+          <t>-1,85; 2,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 4,4</t>
+          <t>-17,91; 4,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 7,99</t>
+          <t>-13,63; 6,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 14,84</t>
+          <t>-7,5; 16,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,64</t>
+          <t>-1,91; 2,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 15,19</t>
+          <t>-14,65; 15,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 28,72</t>
+          <t>-9,09; 31,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 12,62</t>
+          <t>-20,66; 13,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,25</t>
+          <t>-3,93; 1,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 65,78</t>
+          <t>-37,28; 58,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 66,34</t>
+          <t>-14,87; 72,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 25,95</t>
+          <t>-32,89; 28,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,27</t>
+          <t>-3,94; 1,28</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 5,17</t>
+          <t>-22,94; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 13,87</t>
+          <t>-16,46; 13,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 21,83</t>
+          <t>-5,39; 23,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,66</t>
+          <t>1,64; 11,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 12,27</t>
+          <t>-41,34; 12,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 38,36</t>
+          <t>-31,56; 37,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 55,18</t>
+          <t>-9,9; 59,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,23</t>
+          <t>1,69; 13,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 17,48</t>
+          <t>-9,62; 17,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 19,7</t>
+          <t>-11,72; 18,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 14,24</t>
+          <t>-14,2; 15,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 0,0</t>
+          <t>-8,88; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 63,1</t>
+          <t>-24,89; 66,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 54,06</t>
+          <t>-21,66; 50,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 46,91</t>
+          <t>-32,39; 50,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -0,0</t>
+          <t>-8,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,51</t>
+          <t>-17,34; 8,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 13,93</t>
+          <t>-17,75; 15,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 25,03</t>
+          <t>-11,67; 24,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 9,53</t>
+          <t>-5,85; 9,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 20,41</t>
+          <t>-30,29; 20,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 32,5</t>
+          <t>-31,67; 36,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 61,68</t>
+          <t>-19,32; 59,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 10,75</t>
+          <t>-6,01; 10,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 64,07</t>
+          <t>-4,49; 65,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 28,18</t>
+          <t>-20,63; 29,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 24,65</t>
+          <t>-11,29; 26,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,69</t>
+          <t>0,0; 17,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 439,16</t>
+          <t>-11,35; 531,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 76,97</t>
+          <t>-35,43; 75,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 79,37</t>
+          <t>-24,12; 90,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,66</t>
+          <t>0,0; 21,36</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 9,65</t>
+          <t>-21,68; 9,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 11,14</t>
+          <t>-23,91; 11,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 29,07</t>
+          <t>-11,88; 28,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 4,25</t>
+          <t>-10,47; 4,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 27,83</t>
+          <t>-45,63; 28,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 22,22</t>
+          <t>-35,88; 21,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 134,41</t>
+          <t>-29,21; 134,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 4,58</t>
+          <t>-11,04; 4,65</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 5,03</t>
+          <t>-16,48; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 10,89</t>
+          <t>-10,79; 10,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 7,13</t>
+          <t>-12,78; 6,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,21</t>
+          <t>-4,37; 3,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 13,61</t>
+          <t>-34,75; 13,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 22,53</t>
+          <t>-18,48; 21,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 24,05</t>
+          <t>-33,39; 22,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,49</t>
+          <t>-4,46; 4,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 7,62</t>
+          <t>-15,34; 7,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 2,81</t>
+          <t>-17,24; 3,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 8,44</t>
+          <t>-10,5; 7,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 3,14</t>
+          <t>-8,77; 4,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 18,54</t>
+          <t>-31,06; 19,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 8,42</t>
+          <t>-39,69; 10,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 24,9</t>
+          <t>-24,03; 22,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 3,62</t>
+          <t>-9,33; 4,71</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,82</t>
+          <t>-7,75; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,27</t>
+          <t>-6,44; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,31</t>
+          <t>-3,27; 6,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,37</t>
+          <t>-1,76; 2,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 4,36</t>
+          <t>-17,4; 4,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,96</t>
+          <t>-12,96; 7,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,33</t>
+          <t>-7,5; 16,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,53</t>
+          <t>-1,84; 2,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,37%</t>
+          <t>-0,52%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 15,02</t>
+          <t>-14,26; 15,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 31,08</t>
+          <t>-9,83; 29,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 13,33</t>
+          <t>-21,78; 11,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,27</t>
+          <t>-5,54; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 58,91</t>
+          <t>-34,69; 62,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 72,8</t>
+          <t>-14,79; 70,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 28,11</t>
+          <t>-34,57; 23,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,28</t>
+          <t>-5,61; 1,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 5,21</t>
+          <t>-22,26; 6,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 13,77</t>
+          <t>-17,06; 13,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 23,08</t>
+          <t>-5,37; 21,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 11,66</t>
+          <t>1,01; 10,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 12,85</t>
+          <t>-39,92; 16,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 37,65</t>
+          <t>-33,62; 36,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 59,19</t>
+          <t>-9,84; 56,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,29</t>
+          <t>1,05; 11,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,42</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,45%</t>
+          <t>-3,5%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 17,83</t>
+          <t>-10,32; 17,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 18,85</t>
+          <t>-10,9; 20,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 15,65</t>
+          <t>-15,57; 14,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 0,0</t>
+          <t>-9,8; -0,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 66,23</t>
+          <t>-25,98; 62,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 50,04</t>
+          <t>-22,08; 54,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 50,62</t>
+          <t>-34,51; 46,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 0,0</t>
+          <t>-9,86; -0,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 8,6</t>
+          <t>-18,8; 7,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 15,02</t>
+          <t>-17,45; 15,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 24,56</t>
+          <t>-11,15; 25,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 9,23</t>
+          <t>-4,87; 11,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 20,41</t>
+          <t>-32,68; 17,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 36,89</t>
+          <t>-30,87; 37,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 59,12</t>
+          <t>-19,12; 59,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 10,75</t>
+          <t>-4,95; 13,32</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 65,62</t>
+          <t>-6,34; 64,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 29,85</t>
+          <t>-23,51; 30,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 26,51</t>
+          <t>-13,7; 25,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,62</t>
+          <t>0,0; 11,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 531,95</t>
+          <t>-14,09; 434,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 75,53</t>
+          <t>-37,08; 79,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 90,56</t>
+          <t>-26,57; 82,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,36</t>
+          <t>0,0; 12,52</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-2,99%</t>
+          <t>-1,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 9,95</t>
+          <t>-21,82; 10,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 11,1</t>
+          <t>-22,95; 13,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 28,85</t>
+          <t>-13,08; 28,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 4,35</t>
+          <t>-9,32; 4,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 28,19</t>
+          <t>-44,13; 31,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 21,4</t>
+          <t>-33,76; 26,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 134,28</t>
+          <t>-30,83; 141,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 4,65</t>
+          <t>-9,61; 5,42</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,21%</t>
+          <t>-0,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 4,83</t>
+          <t>-14,97; 5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 10,51</t>
+          <t>-10,91; 10,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 6,69</t>
+          <t>-12,81; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,91</t>
+          <t>-4,5; 4,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 13,14</t>
+          <t>-33,12; 16,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 21,47</t>
+          <t>-18,19; 22,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 22,78</t>
+          <t>-34,25; 20,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,18</t>
+          <t>-4,62; 4,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>-2,8%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 7,74</t>
+          <t>-15,7; 7,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 3,29</t>
+          <t>-16,52; 1,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 7,89</t>
+          <t>-10,02; 9,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 4,19</t>
+          <t>-8,29; 3,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 19,68</t>
+          <t>-30,44; 17,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 10,77</t>
+          <t>-39,85; 4,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 22,91</t>
+          <t>-23,32; 26,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,71</t>
+          <t>-8,89; 4,54</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,86</t>
+          <t>-7,88; 1,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,53</t>
+          <t>-6,47; 3,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,24</t>
+          <t>-3,13; 5,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,34</t>
+          <t>-2,24; 2,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,67</t>
+          <t>-17,38; 4,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,64</t>
+          <t>-12,77; 7,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,02</t>
+          <t>-7,61; 14,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,49</t>
+          <t>-2,34; 2,38</t>
         </is>
       </c>
     </row>
